--- a/ig/nr-update-relationship/StructureDefinition-fr-core-related-person.xlsx
+++ b/ig/nr-update-relationship/StructureDefinition-fr-core-related-person.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-18T12:45:56+00:00</t>
+    <t>2024-03-22T10:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -755,31 +755,31 @@
     <t>NK1-3</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson</t>
-  </si>
-  <si>
-    <t>RolePerson</t>
+    <t>RelatedPerson.relationship:Role</t>
+  </si>
+  <si>
+    <t>Role</t>
   </si>
   <si>
     <t>The nature of the relationship. Rôle de la personne. Ex : personne de confiance, aidant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person-role</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RolePerson.id</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-patient-contact-role</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:Role.id</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.id</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.extension</t>
+    <t>RelatedPerson.relationship:Role.extension</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.extension</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding</t>
+    <t>RelatedPerson.relationship:Role.coding</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding</t>
@@ -806,19 +806,19 @@
     <t>C*E.1-8, C*E.10-22</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.id</t>
+    <t>RelatedPerson.relationship:Role.coding.id</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.id</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.extension</t>
+    <t>RelatedPerson.relationship:Role.coding.extension</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.extension</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.system</t>
+    <t>RelatedPerson.relationship:Role.coding.system</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.system</t>
@@ -848,7 +848,7 @@
     <t>C*E.3</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.version</t>
+    <t>RelatedPerson.relationship:Role.coding.version</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.version</t>
@@ -872,7 +872,7 @@
     <t>C*E.7</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.code</t>
+    <t>RelatedPerson.relationship:Role.coding.code</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.code</t>
@@ -899,7 +899,7 @@
     <t>C*E.1</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.display</t>
+    <t>RelatedPerson.relationship:Role.coding.display</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.display</t>
@@ -923,7 +923,7 @@
     <t>C*E.2 - but note this is not well followed</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.coding.userSelected</t>
+    <t>RelatedPerson.relationship:Role.coding.userSelected</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.coding.userSelected</t>
@@ -950,7 +950,7 @@
     <t>Sometimes implied by being first</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RolePerson.text</t>
+    <t>RelatedPerson.relationship:Role.text</t>
   </si>
   <si>
     <t>RelatedPerson.relationship.text</t>
@@ -977,49 +977,52 @@
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RelatedPerson</t>
+    <t>RelatedPerson.relationship:RelationType</t>
+  </si>
+  <si>
+    <t>RelationType</t>
   </si>
   <si>
     <t>The nature of the relationship. Relation de la personne. Ex : Mère, époux, enfant ...</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-related-person</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.id</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.extension</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.id</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.extension</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.system</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-relation-type</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.id</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.extension</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.system</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R216-HL7RoleCode/FHIR/TRE-R216-HL7RoleCode</t>
   </si>
   <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.version</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.code</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.display</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.coding.userSelected</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship:RelatedPerson.text</t>
+    <t>RelatedPerson.relationship:RelationType.coding.version</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.code</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.display</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.coding.userSelected</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship:RelationType.text</t>
   </si>
   <si>
     <t>RelatedPerson.name</t>
@@ -1597,9 +1600,9 @@
   <dimension ref="A1:AM60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="58.84375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.6171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.27734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.31640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="13.0859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1622,7 +1625,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.546875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.12109375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5552,7 +5555,7 @@
         <v>226</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>76</v>
@@ -5577,7 +5580,7 @@
         <v>227</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
         <v>229</v>
@@ -5615,7 +5618,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>76</v>
@@ -5659,7 +5662,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>242</v>
@@ -5768,7 +5771,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>244</v>
@@ -5879,7 +5882,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>246</v>
@@ -5992,7 +5995,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>255</v>
@@ -6101,7 +6104,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>257</v>
@@ -6212,7 +6215,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>259</v>
@@ -6260,7 +6263,7 @@
         <v>76</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>76</v>
@@ -6325,7 +6328,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>269</v>
@@ -6436,7 +6439,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>277</v>
@@ -6549,7 +6552,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>286</v>
@@ -6662,7 +6665,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>294</v>
@@ -6775,7 +6778,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>303</v>
@@ -6888,10 +6891,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6914,19 +6917,19 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>76</v>
@@ -6975,7 +6978,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6990,21 +6993,21 @@
         <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7027,19 +7030,19 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
@@ -7088,7 +7091,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7100,24 +7103,24 @@
         <v>97</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7143,16 +7146,16 @@
         <v>169</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>280</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>76</v>
@@ -7177,13 +7180,13 @@
         <v>76</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>76</v>
@@ -7201,7 +7204,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7216,21 +7219,21 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7253,13 +7256,13 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7310,7 +7313,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7325,7 +7328,7 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7336,10 +7339,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7362,19 +7365,19 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>76</v>
@@ -7423,7 +7426,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7438,21 +7441,21 @@
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7475,19 +7478,19 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7536,7 +7539,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7548,24 +7551,24 @@
         <v>97</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7588,16 +7591,16 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7647,7 +7650,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7659,24 +7662,24 @@
         <v>97</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7699,19 +7702,19 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7760,7 +7763,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7775,7 +7778,7 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>76</v>
@@ -7786,10 +7789,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7895,10 +7898,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8006,14 +8009,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8035,10 +8038,10 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>111</v>
@@ -8093,7 +8096,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8119,10 +8122,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8148,16 +8151,16 @@
         <v>227</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8206,7 +8209,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>85</v>
@@ -8221,21 +8224,21 @@
         <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8261,16 +8264,16 @@
         <v>209</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8319,7 +8322,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8334,7 +8337,7 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>76</v>
